--- a/data/trans_dic/RUIDO_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>67,29; 84,62</t>
+          <t>66,88; 83,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,94; 81,6</t>
+          <t>60,27; 79,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66,5; 80,37</t>
+          <t>65,9; 80,21</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>65,6; 82,09</t>
+          <t>65,8; 81,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,39; 82,43</t>
+          <t>65,23; 82,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,82; 80,75</t>
+          <t>68,9; 80,67</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,49; 90,63</t>
+          <t>65,89; 90,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,9; 78,6</t>
+          <t>61,04; 79,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,2; 85,65</t>
+          <t>66,72; 83,68</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,4; 86,73</t>
+          <t>72,02; 86,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>70,56; 86,51</t>
+          <t>69,64; 86,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,57; 84,37</t>
+          <t>73,45; 84,47</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,94; 83,11</t>
+          <t>72,62; 82,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,78; 78,79</t>
+          <t>69,59; 78,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,56; 79,51</t>
+          <t>72,88; 79,43</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>41903</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51361</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>93263</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>36687; 45963</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>43103; 57161</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83284; 101371</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>65219</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>103469</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>168688</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>57764; 71509</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>88455; 111903</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>153908; 180210</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>78201</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>62581</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>140782</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>65834; 90361</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>54553; 70728</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>126292; 158401</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>71354</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>70883</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>142237</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>64085; 76560</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>62433; 77213</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>131195; 150898</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>256677</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>288294</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>544970</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>240776; 274374</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>268712; 303539</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>523082; 570088</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/RUIDO_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,88; 83,78</t>
+          <t>66,7; 83,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,27; 79,92</t>
+          <t>60,88; 80,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,9; 80,21</t>
+          <t>66,69; 80,46</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>65,8; 81,46</t>
+          <t>65,67; 81,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,23; 82,52</t>
+          <t>65,01; 82,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,9; 80,67</t>
+          <t>68,78; 80,47</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,89; 90,44</t>
+          <t>66,06; 91,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,04; 79,14</t>
+          <t>60,05; 78,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,72; 83,68</t>
+          <t>67,15; 84,49</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,02; 86,04</t>
+          <t>72,51; 86,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,64; 86,13</t>
+          <t>69,98; 85,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,45; 84,47</t>
+          <t>74,1; 84,77</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,62; 82,76</t>
+          <t>73,19; 82,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,59; 78,61</t>
+          <t>69,54; 78,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,88; 79,43</t>
+          <t>72,34; 79,33</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36687; 45963</t>
+          <t>36589; 45964</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43103; 57161</t>
+          <t>43539; 57754</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83284; 101371</t>
+          <t>84283; 101687</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57764; 71509</t>
+          <t>57646; 71294</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88455; 111903</t>
+          <t>88151; 111859</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>153908; 180210</t>
+          <t>153660; 179765</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>65834; 90361</t>
+          <t>66002; 91424</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>54553; 70728</t>
+          <t>53666; 70599</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126292; 158401</t>
+          <t>127103; 159926</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64085; 76560</t>
+          <t>64517; 77109</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62433; 77213</t>
+          <t>62735; 77019</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>131195; 150898</t>
+          <t>132366; 151428</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>240776; 274374</t>
+          <t>242664; 275054</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>268712; 303539</t>
+          <t>268513; 303444</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>523082; 570088</t>
+          <t>519201; 569331</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/RUIDO_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,85%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,7; 83,79</t>
+          <t>60,93; 81,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,88; 80,75</t>
+          <t>66,76; 84,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66,69; 80,46</t>
+          <t>66,52; 80,53</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,76%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>65,67; 81,21</t>
+          <t>65,87; 82,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,01; 82,49</t>
+          <t>65,9; 82,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,78; 80,47</t>
+          <t>69,45; 80,98</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,06; 91,5</t>
+          <t>58,25; 76,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,05; 78,99</t>
+          <t>58,39; 77,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,15; 84,49</t>
+          <t>61,45; 74,83</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,19%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,51; 86,66</t>
+          <t>71,55; 86,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,98; 85,91</t>
+          <t>70,83; 85,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74,1; 84,77</t>
+          <t>73,46; 84,23</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,19; 82,96</t>
+          <t>69,8; 78,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,54; 78,58</t>
+          <t>70,41; 78,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,34; 79,33</t>
+          <t>71,34; 77,37</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>73</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41903</t>
+          <t>49090</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51361</t>
+          <t>42266</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93263</t>
+          <t>91356</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36589; 45964</t>
+          <t>41513; 55763</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43539; 57754</t>
+          <t>37097; 46913</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84283; 101687</t>
+          <t>82285; 99615</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>107</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>65219</t>
+          <t>96518</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>103469</t>
+          <t>64685</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>168688</t>
+          <t>161203</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57646; 71294</t>
+          <t>83020; 103942</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88151; 111859</t>
+          <t>57170; 71528</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>153660; 179765</t>
+          <t>147782; 172316</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>78201</t>
+          <t>54545</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62581</t>
+          <t>49240</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140782</t>
+          <t>103785</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>66002; 91424</t>
+          <t>46759; 61580</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>53666; 70599</t>
+          <t>41787; 55607</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>127103; 159926</t>
+          <t>93304; 113623</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>100</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>71354</t>
+          <t>66457</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>70883</t>
+          <t>68491</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142237</t>
+          <t>134949</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64517; 77109</t>
+          <t>59764; 72345</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62735; 77019</t>
+          <t>61544; 74330</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>132366; 151428</t>
+          <t>125187; 143543</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>351</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>256677</t>
+          <t>266611</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>288294</t>
+          <t>224681</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>544970</t>
+          <t>491292</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>242664; 275054</t>
+          <t>249873; 282316</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>268513; 303444</t>
+          <t>211785; 236506</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>519201; 569331</t>
+          <t>469918; 509658</t>
         </is>
       </c>
     </row>
